--- a/data/Flow01/testsExport.xlsx
+++ b/data/Flow01/testsExport.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,12 +471,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>10:32:12.618000</t>
+          <t>2026-03-16 14:50:57.904000</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0643d7f2c5741f17fa65fb6d7d9a71d1</t>
+          <t>631397bb57df581f452a161263bedc6e</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -500,225 +500,15 @@
       <c r="G2" t="n">
         <v>0</v>
       </c>
-      <c r="H2" t="n">
-        <v>70568</v>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>70568</t>
+        </is>
       </c>
       <c r="I2" t="n">
         <v>34</v>
       </c>
       <c r="J2" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>10:33:41.450000</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>0643d7f2c5741f17fa65fb6d7d9a71d1</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>4d07e1568cd1bb8f15134b69a48526bb</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>c85fb5d97bc71baa9df77e077ec3b2c8</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> - tax_class - post_content - post_password - post_content_filtered - </t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>70568</v>
-      </c>
-      <c r="I3" t="n">
-        <v>34</v>
-      </c>
-      <c r="J3" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-03-16 10:46:15.577000</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>0643d7f2c5741f17fa65fb6d7d9a71d1</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>4d07e1568cd1bb8f15134b69a48526bb</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>c85fb5d97bc71baa9df77e077ec3b2c8</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> - tax_class - post_content - post_password - post_content_filtered - </t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>70568</v>
-      </c>
-      <c r="I4" t="n">
-        <v>34</v>
-      </c>
-      <c r="J4" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-03-16 10:47:51.638000</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>f69716deaeae87f3970042789e3e33a2</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>4d07e1568cd1bb8f15134b69a48526bb</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>c85fb5d97bc71baa9df77e077ec3b2c8</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> - tax_class - post_content - post_password - post_content_filtered - </t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>70568</v>
-      </c>
-      <c r="I5" t="n">
-        <v>34</v>
-      </c>
-      <c r="J5" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-03-16 10:49:19.151000</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>0643d7f2c5741f17fa65fb6d7d9a71d1</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>058c65f29a937c82c9f80d3f656dabcc</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>c85fb5d97bc71baa9df77e077ec3b2c8</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> - tax_class - post_content - post_password - post_content_filtered - </t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>70568</v>
-      </c>
-      <c r="I6" t="n">
-        <v>34</v>
-      </c>
-      <c r="J6" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-03-16 10:54:07.746000</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>0643d7f2c5741f17fa65fb6d7d9a71d1</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>db669c29cca03f5450e3f05d70c97c86</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>c85fb5d97bc71baa9df77e077ec3b2c8</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> - tax_class - post_content - post_password - post_content_filtered - </t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>70928</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>34</v>
-      </c>
-      <c r="J7" t="n">
         <v>30</v>
       </c>
     </row>

--- a/data/Flow01/testsExport.xlsx
+++ b/data/Flow01/testsExport.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,15 +500,351 @@
       <c r="G2" t="n">
         <v>0</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>70568</t>
-        </is>
+      <c r="H2" t="n">
+        <v>70568</v>
       </c>
       <c r="I2" t="n">
         <v>34</v>
       </c>
       <c r="J2" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-03-24 11:06:10.096000</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>631397bb57df581f452a161263bedc6e</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>4d07e1568cd1bb8f15134b69a48526bb</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>c85fb5d97bc71baa9df77e077ec3b2c8</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - tax_class - post_content - post_password - post_content_filtered - </t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>70568</v>
+      </c>
+      <c r="I3" t="n">
+        <v>34</v>
+      </c>
+      <c r="J3" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-03-24 12:12:39.924000</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>631397bb57df581f452a161263bedc6e</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>4d07e1568cd1bb8f15134b69a48526bb</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>c85fb5d97bc71baa9df77e077ec3b2c8</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - tax_class - post_content - post_password - post_content_filtered - </t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>70568</v>
+      </c>
+      <c r="I4" t="n">
+        <v>34</v>
+      </c>
+      <c r="J4" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-03-24 12:14:55.744000</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>631397bb57df581f452a161263bedc6e</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>4d07e1568cd1bb8f15134b69a48526bb</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>c85fb5d97bc71baa9df77e077ec3b2c8</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - tax_class - post_content - post_password - post_content_filtered - </t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>70568</v>
+      </c>
+      <c r="I5" t="n">
+        <v>34</v>
+      </c>
+      <c r="J5" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-03-24 12:32:25.512000</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>631397bb57df581f452a161263bedc6e</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>4d07e1568cd1bb8f15134b69a48526bb</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>c85fb5d97bc71baa9df77e077ec3b2c8</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - tax_class - post_content - post_password - post_content_filtered - </t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>70568</v>
+      </c>
+      <c r="I6" t="n">
+        <v>34</v>
+      </c>
+      <c r="J6" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-03-24 12:37:15.527000</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>631397bb57df581f452a161263bedc6e</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>4d07e1568cd1bb8f15134b69a48526bb</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>c85fb5d97bc71baa9df77e077ec3b2c8</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - tax_class - post_content - post_password - post_content_filtered - </t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>70568</v>
+      </c>
+      <c r="I7" t="n">
+        <v>34</v>
+      </c>
+      <c r="J7" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-03-24 12:54:21.506000</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>631397bb57df581f452a161263bedc6e</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>4d07e1568cd1bb8f15134b69a48526bb</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>c85fb5d97bc71baa9df77e077ec3b2c8</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - tax_class - post_content - post_password - post_content_filtered - </t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>70568</v>
+      </c>
+      <c r="I8" t="n">
+        <v>34</v>
+      </c>
+      <c r="J8" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-03-24 12:55:07.965000</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>631397bb57df581f452a161263bedc6e</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>4d07e1568cd1bb8f15134b69a48526bb</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>c85fb5d97bc71baa9df77e077ec3b2c8</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - tax_class - post_content - post_password - post_content_filtered - </t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>70568</v>
+      </c>
+      <c r="I9" t="n">
+        <v>34</v>
+      </c>
+      <c r="J9" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-03-24 12:58:46.884000</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>631397bb57df581f452a161263bedc6e</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>4d07e1568cd1bb8f15134b69a48526bb</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>c85fb5d97bc71baa9df77e077ec3b2c8</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - tax_class - post_content - post_password - post_content_filtered - </t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>70568</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>34</v>
+      </c>
+      <c r="J10" t="n">
         <v>30</v>
       </c>
     </row>
